--- a/Strengthentable.xlsx
+++ b/Strengthentable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\SBSAcademy_Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E18F37-51D3-4FDD-ACF1-CF3EE3B2EE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8905753-7E47-44A0-9BC5-6DB6E7070543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3C30DD39-C5F1-46AF-B8AF-3163B90A8E32}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Raritytable" sheetId="8" r:id="rId3"/>
     <sheet name="FusionStrengthentable" sheetId="11" r:id="rId4"/>
     <sheet name="FusionArtifacttable" sheetId="12" r:id="rId5"/>
+    <sheet name="Enumtable" sheetId="13" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,6 +48,8 @@
   <authors>
     <author>tc={56F6E92E-0E24-44B6-9316-0334386F1F5D}</author>
     <author>tc={E959BAEB-297A-4BE5-AF05-78B592B6E732}</author>
+    <author>tc={8E431D54-2462-4024-A33B-A5E922FB57E1}</author>
+    <author>tc={D31543E9-13D8-48A6-A7C7-25FB9EBE8191}</author>
   </authors>
   <commentList>
     <comment ref="D7" authorId="0" shapeId="0" xr:uid="{56F6E92E-0E24-44B6-9316-0334386F1F5D}">
@@ -63,6 +66,40 @@
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
 댓글:
     부정적인 효과만 주는 증강</t>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="2" shapeId="0" xr:uid="{8E431D54-2462-4024-A33B-A5E922FB57E1}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    이속증가 / 공속 감소</t>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="3" shapeId="0" xr:uid="{D31543E9-13D8-48A6-A7C7-25FB9EBE8191}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    보스 추가 데미지 / 일반 데미지 감소</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={6D2338D0-3E26-4F40-BE16-5F7ADF8A6334}</author>
+  </authors>
+  <commentList>
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{6D2338D0-3E26-4F40-BE16-5F7ADF8A6334}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    저주의 등급화 필요?</t>
       </text>
     </comment>
   </commentList>
@@ -92,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="118">
   <si>
     <t>num</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -284,7 +321,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Category</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Streng_Category</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>증강 적용 대상</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -517,6 +562,30 @@
   </si>
   <si>
     <t>강강약약</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target_Scope</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유물 적용 대상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저주</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Curse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -652,7 +721,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -693,6 +762,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1043,6 +1115,20 @@
   <threadedComment ref="D8" dT="2026-10-22T02:48:08.25" personId="{2EA3F17D-ABCE-463C-ADF1-0C3F21511564}" id="{E959BAEB-297A-4BE5-AF05-78B592B6E732}">
     <text>부정적인 효과만 주는 증강</text>
   </threadedComment>
+  <threadedComment ref="D10" dT="2026-10-22T05:03:15.47" personId="{2EA3F17D-ABCE-463C-ADF1-0C3F21511564}" id="{8E431D54-2462-4024-A33B-A5E922FB57E1}">
+    <text>이속증가 / 공속 감소</text>
+  </threadedComment>
+  <threadedComment ref="D11" dT="2026-10-22T05:02:56.33" personId="{2EA3F17D-ABCE-463C-ADF1-0C3F21511564}" id="{D31543E9-13D8-48A6-A7C7-25FB9EBE8191}">
+    <text>보스 추가 데미지 / 일반 데미지 감소</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E10" dT="2026-10-22T05:00:28.82" personId="{2EA3F17D-ABCE-463C-ADF1-0C3F21511564}" id="{6D2338D0-3E26-4F40-BE16-5F7ADF8A6334}">
+    <text>저주의 등급화 필요?</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -1052,7 +1138,7 @@
   <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.875" style="1" bestFit="1" customWidth="1"/>
@@ -1085,19 +1171,19 @@
         <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>31</v>
@@ -1106,7 +1192,7 @@
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1135,13 +1221,13 @@
         <v>29</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>30</v>
@@ -1167,14 +1253,9 @@
         <v>40001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="K3" s="14"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="str">
@@ -1187,14 +1268,9 @@
         <v>40002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>59</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="K4" s="14"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
@@ -1207,13 +1283,7 @@
         <v>40003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1227,13 +1297,10 @@
         <v>40004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>55</v>
+        <v>101</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1247,10 +1314,7 @@
         <v>40005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1264,10 +1328,10 @@
         <v>40006</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>61</v>
+        <v>108</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1281,10 +1345,7 @@
         <v>40007</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1298,7 +1359,7 @@
         <v>40008</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1312,7 +1373,7 @@
         <v>40009</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1327,19 +1388,19 @@
   <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.75" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.25" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
@@ -1348,40 +1409,40 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1392,40 +1453,40 @@
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -1442,13 +1503,13 @@
         <v>50001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1462,13 +1523,13 @@
         <v>50002</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -1482,13 +1543,13 @@
         <v>50003</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1502,13 +1563,13 @@
         <v>50004</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1522,20 +1583,20 @@
         <v>50005</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J8" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="J9" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1545,7 +1606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DBE53E-B5E9-4775-B9E7-27E06441A3E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DBE53E-B5E9-4775-B9E7-27E06441A3E0}">
   <dimension ref="A1:G100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1604,7 +1665,7 @@
         <v>RarityData</v>
       </c>
       <c r="B3" s="8" cm="1">
-        <f t="array" ref="B3:B9">IF(COUNTA(C3:C1000)=0, "", _xlfn.SEQUENCE(COUNTA(C3:C1000)))</f>
+        <f t="array" ref="B3:B10">IF(COUNTA(C3:C1000)=0, "", _xlfn.SEQUENCE(COUNTA(C3:C1000)))</f>
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
@@ -1721,7 +1782,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
-        <v/>
+        <v>RarityData</v>
+      </c>
+      <c r="B10" s="1">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2177,6 +2250,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2188,7 +2262,7 @@
     <col min="1" max="1" width="12.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.125" style="1" customWidth="1"/>
     <col min="7" max="7" width="16.875" style="1" bestFit="1" customWidth="1"/>
@@ -2229,16 +2303,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
@@ -2258,22 +2332,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
@@ -2377,16 +2451,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
@@ -2412,16 +2486,16 @@
         <v>9</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
@@ -2474,4 +2548,82 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7CEA66E-784C-4BD6-9B91-6ACE51841782}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.625" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Strengthentable.xlsx
+++ b/Strengthentable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\SBSAcademy_Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8905753-7E47-44A0-9BC5-6DB6E7070543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB1AC05-939D-4443-9AFA-D54F715908AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3C30DD39-C5F1-46AF-B8AF-3163B90A8E32}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{3C30DD39-C5F1-46AF-B8AF-3163B90A8E32}"/>
   </bookViews>
   <sheets>
     <sheet name="Strengthentable" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="133">
   <si>
     <t>num</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -586,6 +586,66 @@
   </si>
   <si>
     <t>?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*0.7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*0.8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>*0.9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기믹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전판 == 획득한 특수 재화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>후판으로 이식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>백신 좀비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘리트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>백신맞은 반좀비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>좀비변신</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>인간</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫 슬롯</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -593,7 +653,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -616,12 +676,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1379,7 +1433,8 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1607,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8DBE53E-B5E9-4775-B9E7-27E06441A3E0}">
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" bestFit="1" customWidth="1"/>
@@ -1616,10 +1671,12 @@
     <col min="4" max="4" width="12.25" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="16.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="8" max="20" width="9" style="1"/>
+    <col min="21" max="21" width="15.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="33" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
         <v>35</v>
       </c>
@@ -1635,8 +1692,14 @@
       <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="T1" s="1">
+        <v>1</v>
+      </c>
+      <c r="U1" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1658,8 +1721,26 @@
       <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="str" cm="1">
         <f t="array" ref="A3:A100">IF(C3:C100="","", "RarityData")</f>
         <v>RarityData</v>
@@ -1677,8 +1758,20 @@
       <c r="E3" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K3" s="1">
+        <v>60</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -1694,8 +1787,14 @@
       <c r="E4" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K4" s="1">
+        <v>23</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -1711,8 +1810,17 @@
       <c r="E5" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K5" s="1">
+        <v>11</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -1728,8 +1836,17 @@
       <c r="E6" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K6" s="1">
+        <v>4</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -1745,8 +1862,26 @@
       <c r="E7" s="1">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I7" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="M7" s="1">
+        <v>25</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -1762,8 +1897,14 @@
       <c r="E8" s="1">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K8" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="M8" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -1779,8 +1920,11 @@
       <c r="E9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="str">
         <v>RarityData</v>
       </c>
@@ -1797,32 +1941,32 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="str">
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="str">
         <v/>
       </c>
